--- a/AAII_Financials/Quarterly/MGN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MGN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="92">
   <si>
     <t>MGN</t>
   </si>
@@ -1924,10 +1924,10 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>15400</v>
+        <v>7200</v>
       </c>
       <c r="E42" s="3">
-        <v>14900</v>
+        <v>6900</v>
       </c>
       <c r="F42" s="3">
         <v>5400</v>
@@ -2046,11 +2046,11 @@
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>8</v>
+      <c r="D45" s="3">
+        <v>8200</v>
+      </c>
+      <c r="E45" s="3">
+        <v>7900</v>
       </c>
       <c r="F45" s="3">
         <v>16900</v>
@@ -2573,10 +2573,10 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>6700</v>
+        <v>10300</v>
       </c>
       <c r="E59" s="3">
-        <v>6400</v>
+        <v>10000</v>
       </c>
       <c r="F59" s="3">
         <v>14300</v>
